--- a/truth_table.xlsx
+++ b/truth_table.xlsx
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -668,13 +668,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -782,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
